--- a/01_My_Learnings/05_NSO_work/02_RC_Cleaning/02_meta_data/Meta_Data.xlsx
+++ b/01_My_Learnings/05_NSO_work/02_RC_Cleaning/02_meta_data/Meta_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grv\Desktop\RC_Cleaning\02_meta_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\01_My_Learnings\05_NSO_work\02_RC_Cleaning\02_meta_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8790E813-CA64-4095-B523-5E2ABE794911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7896A5-3A00-4938-B77A-66AC9F6FD59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4836" yWindow="2856" windowWidth="17280" windowHeight="8880" tabRatio="789" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" tabRatio="789" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="state" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>crop_cd</t>
   </si>
@@ -60,57 +60,15 @@
     <t>ccf</t>
   </si>
   <si>
-    <t>Paddy_I</t>
-  </si>
-  <si>
-    <t>Jowar</t>
-  </si>
-  <si>
     <t>Bajra</t>
   </si>
   <si>
-    <t>Maize</t>
-  </si>
-  <si>
-    <t>Groundnut</t>
-  </si>
-  <si>
-    <t>Gingelly</t>
-  </si>
-  <si>
-    <t>Redgram</t>
-  </si>
-  <si>
-    <t>Cotton</t>
-  </si>
-  <si>
-    <t>Paddy_II</t>
-  </si>
-  <si>
-    <t>Sugarcane</t>
-  </si>
-  <si>
     <t>season_cd</t>
   </si>
   <si>
     <t>season_nm</t>
   </si>
   <si>
-    <t>Kharif</t>
-  </si>
-  <si>
-    <t>E.Kharif</t>
-  </si>
-  <si>
-    <t>L.Kharif</t>
-  </si>
-  <si>
-    <t>Phase-I</t>
-  </si>
-  <si>
-    <t>Phase-II</t>
-  </si>
-  <si>
     <t>ddg</t>
   </si>
   <si>
@@ -126,9 +84,6 @@
     <t>year</t>
   </si>
   <si>
-    <t>Tamil Nadu</t>
-  </si>
-  <si>
     <t>novp</t>
   </si>
   <si>
@@ -145,12 +100,33 @@
   </si>
   <si>
     <t>State</t>
+  </si>
+  <si>
+    <t>Gujarat</t>
+  </si>
+  <si>
+    <t>Rabi</t>
+  </si>
+  <si>
+    <t>Summer</t>
+  </si>
+  <si>
+    <t>Rape n Mustard</t>
+  </si>
+  <si>
+    <t>Gram</t>
+  </si>
+  <si>
+    <t>Wheat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -195,9 +171,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,29 +459,29 @@
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>33</v>
-      </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>2024</v>
@@ -521,33 +498,33 @@
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -561,31 +538,31 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -602,114 +579,114 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="D2">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="E2">
-        <v>2510</v>
+        <v>1001</v>
       </c>
       <c r="F2">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="D3">
-        <v>234</v>
+        <v>325</v>
       </c>
       <c r="E3">
-        <v>2510</v>
+        <v>1001</v>
       </c>
       <c r="F3">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="D4">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="E4">
-        <v>2501</v>
+        <v>1004</v>
       </c>
       <c r="F4">
-        <v>2801</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="D5">
-        <v>227</v>
+        <v>323</v>
       </c>
       <c r="E5">
-        <v>2501</v>
+        <v>1004</v>
       </c>
       <c r="F5">
-        <v>2801</v>
+        <v>1504</v>
       </c>
     </row>
   </sheetData>
@@ -722,163 +699,51 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
-      </c>
       <c r="B5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>3</v>
-      </c>
-      <c r="B16">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>3</v>
-      </c>
-      <c r="B17">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>3</v>
-      </c>
-      <c r="B18">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>3</v>
-      </c>
-      <c r="B19">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -891,43 +756,35 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -940,17 +797,18 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -959,213 +817,93 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>40</v>
+        <v>22</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.4</v>
       </c>
       <c r="E2">
         <v>40</v>
       </c>
       <c r="F2">
-        <v>0.24364</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.38269999999999998</v>
+      </c>
+      <c r="E3">
+        <v>60</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.38129999999999997</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>40</v>
-      </c>
-      <c r="E3">
-        <v>40</v>
-      </c>
-      <c r="F3">
-        <v>0.28720000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>40</v>
-      </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
-      <c r="F4">
-        <v>0.31452000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
       <c r="B5">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>40</v>
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.38080000000000003</v>
       </c>
       <c r="E5">
         <v>40</v>
       </c>
       <c r="F5">
-        <v>0.29511999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6">
         <v>40</v>
-      </c>
-      <c r="E6">
-        <v>40</v>
-      </c>
-      <c r="F6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>40</v>
-      </c>
-      <c r="F7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8">
-        <v>40</v>
-      </c>
-      <c r="E8">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>6.59E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9">
-        <v>40</v>
-      </c>
-      <c r="E9">
-        <v>40</v>
-      </c>
-      <c r="F9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10">
-        <v>40</v>
-      </c>
-      <c r="E10">
-        <v>40</v>
-      </c>
-      <c r="F10">
-        <v>0.24939913599999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>92</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11">
-        <v>60</v>
-      </c>
-      <c r="E11">
-        <v>60</v>
-      </c>
-      <c r="F11">
-        <v>0.24865243200000001</v>
       </c>
     </row>
   </sheetData>
